--- a/public/plantilla-equipos.xlsx
+++ b/public/plantilla-equipos.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="600" firstSheet="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Maquinaria y Equipos" sheetId="1" state="visible" r:id="rId1"/>
@@ -16,10 +16,10 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="2">
-    <numFmt numFmtId="165" formatCode="&quot;$&quot;#,##0;[Red]\-&quot;$&quot;#,##0"/>
-    <numFmt numFmtId="166" formatCode="0.0%"/>
+    <numFmt numFmtId="164" formatCode="&quot;$&quot;#,##0;[Red]\-&quot;$&quot;#,##0"/>
+    <numFmt numFmtId="165" formatCode="0.0%"/>
   </numFmts>
-  <fonts count="12">
+  <fonts count="14">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -103,6 +103,17 @@
       <b val="1"/>
       <sz val="10"/>
     </font>
+    <font>
+      <name val="Calibri"/>
+      <color rgb="FF000000"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="FF000000"/>
+      <sz val="10"/>
+    </font>
   </fonts>
   <fills count="10">
     <fill>
@@ -299,7 +310,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="91">
+  <cellXfs count="104">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -319,47 +330,47 @@
     <xf numFmtId="14" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="2" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="165" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="2" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="165" fontId="2" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="165" fontId="6" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="166" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="6" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="166" fontId="2" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="166" fontId="2" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="166" fontId="6" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="4" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="166" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="165" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -407,17 +418,17 @@
     <xf numFmtId="0" fontId="7" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="165" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="166" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -430,7 +441,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="2" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="2" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="4" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -445,13 +456,13 @@
     <xf numFmtId="0" fontId="0" fillId="7" borderId="9" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="10" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="11" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="2" fillId="4" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="2" fillId="4" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="2" fillId="4" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="2" fillId="4" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="2" fillId="4" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="2" fillId="4" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="6" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -481,10 +492,10 @@
     <xf numFmtId="0" fontId="2" fillId="6" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="166" fontId="2" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="165" fontId="2" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="2" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -502,13 +513,13 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="166" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="165" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="166" fontId="6" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="165" fontId="6" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -518,7 +529,7 @@
     <xf numFmtId="0" fontId="6" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="6" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="6" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="9" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -531,6 +542,49 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="10" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="164" fontId="12" fillId="0" borderId="1" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="4" fontId="12" fillId="0" borderId="1" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="164" fontId="2" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="13" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="12" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="2" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1044,10 +1098,10 @@
       </c>
       <c r="B10" s="90" t="n"/>
       <c r="C10" s="84" t="n"/>
-      <c r="D10" s="24" t="n"/>
-      <c r="E10" s="90" t="n"/>
-      <c r="F10" s="90" t="n"/>
-      <c r="G10" s="84" t="n"/>
+      <c r="D10" s="91" t="n"/>
+      <c r="E10" s="92" t="n"/>
+      <c r="F10" s="92" t="n"/>
+      <c r="G10" s="93" t="n"/>
       <c r="H10" s="22" t="inlineStr">
         <is>
           <t>Tipo de proyecto</t>
@@ -1055,10 +1109,10 @@
       </c>
       <c r="I10" s="90" t="n"/>
       <c r="J10" s="84" t="n"/>
-      <c r="K10" s="24" t="n"/>
-      <c r="L10" s="90" t="n"/>
-      <c r="M10" s="90" t="n"/>
-      <c r="N10" s="84" t="n"/>
+      <c r="K10" s="91" t="n"/>
+      <c r="L10" s="92" t="n"/>
+      <c r="M10" s="92" t="n"/>
+      <c r="N10" s="93" t="n"/>
     </row>
     <row r="11" ht="18" customHeight="1" s="34">
       <c r="A11" s="22" t="inlineStr">
@@ -1068,10 +1122,10 @@
       </c>
       <c r="B11" s="90" t="n"/>
       <c r="C11" s="84" t="n"/>
-      <c r="D11" s="24" t="n"/>
-      <c r="E11" s="90" t="n"/>
-      <c r="F11" s="90" t="n"/>
-      <c r="G11" s="84" t="n"/>
+      <c r="D11" s="91" t="n"/>
+      <c r="E11" s="92" t="n"/>
+      <c r="F11" s="92" t="n"/>
+      <c r="G11" s="93" t="n"/>
       <c r="H11" s="22" t="inlineStr">
         <is>
           <t>Contratante</t>
@@ -1079,10 +1133,10 @@
       </c>
       <c r="I11" s="90" t="n"/>
       <c r="J11" s="84" t="n"/>
-      <c r="K11" s="24" t="n"/>
-      <c r="L11" s="90" t="n"/>
-      <c r="M11" s="90" t="n"/>
-      <c r="N11" s="84" t="n"/>
+      <c r="K11" s="91" t="n"/>
+      <c r="L11" s="92" t="n"/>
+      <c r="M11" s="92" t="n"/>
+      <c r="N11" s="93" t="n"/>
     </row>
     <row r="12" ht="18" customHeight="1" s="34">
       <c r="A12" s="22" t="inlineStr">
@@ -1092,10 +1146,10 @@
       </c>
       <c r="B12" s="90" t="n"/>
       <c r="C12" s="84" t="n"/>
-      <c r="D12" s="24" t="n"/>
-      <c r="E12" s="90" t="n"/>
-      <c r="F12" s="90" t="n"/>
-      <c r="G12" s="84" t="n"/>
+      <c r="D12" s="91" t="n"/>
+      <c r="E12" s="92" t="n"/>
+      <c r="F12" s="92" t="n"/>
+      <c r="G12" s="93" t="n"/>
       <c r="H12" s="22" t="inlineStr">
         <is>
           <t>Responsable del control</t>
@@ -1103,10 +1157,10 @@
       </c>
       <c r="I12" s="90" t="n"/>
       <c r="J12" s="84" t="n"/>
-      <c r="K12" s="24" t="n"/>
-      <c r="L12" s="90" t="n"/>
-      <c r="M12" s="90" t="n"/>
-      <c r="N12" s="84" t="n"/>
+      <c r="K12" s="91" t="n"/>
+      <c r="L12" s="92" t="n"/>
+      <c r="M12" s="92" t="n"/>
+      <c r="N12" s="93" t="n"/>
     </row>
     <row r="13" ht="15" customHeight="1" s="34">
       <c r="A13" s="40" t="inlineStr">
@@ -1201,340 +1255,340 @@
       </c>
     </row>
     <row r="15" ht="22.05" customHeight="1" s="34">
-      <c r="A15" s="5" t="n">
+      <c r="A15" s="94" t="n">
         <v>1</v>
       </c>
-      <c r="B15" s="24" t="n"/>
-      <c r="C15" s="24" t="n"/>
-      <c r="D15" s="5" t="n"/>
-      <c r="E15" s="24" t="n"/>
-      <c r="F15" s="24" t="n"/>
-      <c r="G15" s="5" t="n"/>
-      <c r="H15" s="7" t="n"/>
-      <c r="I15" s="20" t="n"/>
-      <c r="J15" s="8">
+      <c r="B15" s="91" t="n"/>
+      <c r="C15" s="91" t="n"/>
+      <c r="D15" s="95" t="n"/>
+      <c r="E15" s="91" t="n"/>
+      <c r="F15" s="91" t="n"/>
+      <c r="G15" s="95" t="n"/>
+      <c r="H15" s="96" t="n"/>
+      <c r="I15" s="97" t="n"/>
+      <c r="J15" s="98">
         <f>IF(OR(H15="",I15=""),"",H15*I15)</f>
         <v/>
       </c>
-      <c r="K15" s="7" t="n"/>
-      <c r="L15" s="7" t="n"/>
-      <c r="M15" s="8">
+      <c r="K15" s="96" t="n"/>
+      <c r="L15" s="96" t="n"/>
+      <c r="M15" s="98">
         <f>IF(J15="","",J15+N(K15)+N(L15))</f>
         <v/>
       </c>
-      <c r="N15" s="24" t="n"/>
+      <c r="N15" s="91" t="n"/>
     </row>
     <row r="16" ht="22.05" customHeight="1" s="34">
-      <c r="A16" s="5" t="n">
+      <c r="A16" s="94" t="n">
         <v>2</v>
       </c>
-      <c r="B16" s="24" t="n"/>
-      <c r="C16" s="24" t="n"/>
-      <c r="D16" s="5" t="n"/>
-      <c r="E16" s="24" t="n"/>
-      <c r="F16" s="24" t="n"/>
-      <c r="G16" s="5" t="n"/>
-      <c r="H16" s="7" t="n"/>
-      <c r="I16" s="20" t="n"/>
-      <c r="J16" s="8">
+      <c r="B16" s="91" t="n"/>
+      <c r="C16" s="91" t="n"/>
+      <c r="D16" s="95" t="n"/>
+      <c r="E16" s="91" t="n"/>
+      <c r="F16" s="91" t="n"/>
+      <c r="G16" s="95" t="n"/>
+      <c r="H16" s="96" t="n"/>
+      <c r="I16" s="97" t="n"/>
+      <c r="J16" s="98">
         <f>IF(OR(H16="",I16=""),"",H16*I16)</f>
         <v/>
       </c>
-      <c r="K16" s="7" t="n"/>
-      <c r="L16" s="7" t="n"/>
-      <c r="M16" s="8">
+      <c r="K16" s="96" t="n"/>
+      <c r="L16" s="96" t="n"/>
+      <c r="M16" s="98">
         <f>IF(J16="","",J16+N(K16)+N(L16))</f>
         <v/>
       </c>
-      <c r="N16" s="24" t="n"/>
+      <c r="N16" s="91" t="n"/>
     </row>
     <row r="17" ht="22.05" customHeight="1" s="34">
-      <c r="A17" s="5" t="n">
+      <c r="A17" s="94" t="n">
         <v>3</v>
       </c>
-      <c r="B17" s="24" t="n"/>
-      <c r="C17" s="24" t="n"/>
-      <c r="D17" s="5" t="n"/>
-      <c r="E17" s="24" t="n"/>
-      <c r="F17" s="24" t="n"/>
-      <c r="G17" s="5" t="n"/>
-      <c r="H17" s="7" t="n"/>
-      <c r="I17" s="20" t="n"/>
-      <c r="J17" s="8">
+      <c r="B17" s="91" t="n"/>
+      <c r="C17" s="91" t="n"/>
+      <c r="D17" s="95" t="n"/>
+      <c r="E17" s="91" t="n"/>
+      <c r="F17" s="91" t="n"/>
+      <c r="G17" s="95" t="n"/>
+      <c r="H17" s="96" t="n"/>
+      <c r="I17" s="97" t="n"/>
+      <c r="J17" s="98">
         <f>IF(OR(H17="",I17=""),"",H17*I17)</f>
         <v/>
       </c>
-      <c r="K17" s="7" t="n"/>
-      <c r="L17" s="7" t="n"/>
-      <c r="M17" s="8">
+      <c r="K17" s="96" t="n"/>
+      <c r="L17" s="96" t="n"/>
+      <c r="M17" s="98">
         <f>IF(J17="","",J17+N(K17)+N(L17))</f>
         <v/>
       </c>
-      <c r="N17" s="24" t="n"/>
+      <c r="N17" s="91" t="n"/>
     </row>
     <row r="18" ht="22.05" customHeight="1" s="34">
-      <c r="A18" s="5" t="n">
+      <c r="A18" s="94" t="n">
         <v>4</v>
       </c>
-      <c r="B18" s="24" t="n"/>
-      <c r="C18" s="24" t="n"/>
-      <c r="D18" s="5" t="n"/>
-      <c r="E18" s="24" t="n"/>
-      <c r="F18" s="24" t="n"/>
-      <c r="G18" s="5" t="n"/>
-      <c r="H18" s="7" t="n"/>
-      <c r="I18" s="20" t="n"/>
-      <c r="J18" s="8">
+      <c r="B18" s="91" t="n"/>
+      <c r="C18" s="91" t="n"/>
+      <c r="D18" s="95" t="n"/>
+      <c r="E18" s="91" t="n"/>
+      <c r="F18" s="91" t="n"/>
+      <c r="G18" s="95" t="n"/>
+      <c r="H18" s="96" t="n"/>
+      <c r="I18" s="97" t="n"/>
+      <c r="J18" s="98">
         <f>IF(OR(H18="",I18=""),"",H18*I18)</f>
         <v/>
       </c>
-      <c r="K18" s="7" t="n"/>
-      <c r="L18" s="7" t="n"/>
-      <c r="M18" s="8">
+      <c r="K18" s="96" t="n"/>
+      <c r="L18" s="96" t="n"/>
+      <c r="M18" s="98">
         <f>IF(J18="","",J18+N(K18)+N(L18))</f>
         <v/>
       </c>
-      <c r="N18" s="24" t="n"/>
+      <c r="N18" s="91" t="n"/>
     </row>
     <row r="19" ht="22.05" customHeight="1" s="34">
-      <c r="A19" s="5" t="n">
+      <c r="A19" s="94" t="n">
         <v>5</v>
       </c>
-      <c r="B19" s="24" t="n"/>
-      <c r="C19" s="24" t="n"/>
-      <c r="D19" s="5" t="n"/>
-      <c r="E19" s="24" t="n"/>
-      <c r="F19" s="24" t="n"/>
-      <c r="G19" s="5" t="n"/>
-      <c r="H19" s="7" t="n"/>
-      <c r="I19" s="20" t="n"/>
-      <c r="J19" s="8">
+      <c r="B19" s="91" t="n"/>
+      <c r="C19" s="91" t="n"/>
+      <c r="D19" s="95" t="n"/>
+      <c r="E19" s="91" t="n"/>
+      <c r="F19" s="91" t="n"/>
+      <c r="G19" s="95" t="n"/>
+      <c r="H19" s="96" t="n"/>
+      <c r="I19" s="97" t="n"/>
+      <c r="J19" s="98">
         <f>IF(OR(H19="",I19=""),"",H19*I19)</f>
         <v/>
       </c>
-      <c r="K19" s="7" t="n"/>
-      <c r="L19" s="7" t="n"/>
-      <c r="M19" s="8">
+      <c r="K19" s="96" t="n"/>
+      <c r="L19" s="96" t="n"/>
+      <c r="M19" s="98">
         <f>IF(J19="","",J19+N(K19)+N(L19))</f>
         <v/>
       </c>
-      <c r="N19" s="24" t="n"/>
+      <c r="N19" s="91" t="n"/>
     </row>
     <row r="20" ht="22.05" customHeight="1" s="34">
-      <c r="A20" s="5" t="n">
+      <c r="A20" s="94" t="n">
         <v>6</v>
       </c>
-      <c r="B20" s="24" t="n"/>
-      <c r="C20" s="24" t="n"/>
-      <c r="D20" s="5" t="n"/>
-      <c r="E20" s="24" t="n"/>
-      <c r="F20" s="24" t="n"/>
-      <c r="G20" s="5" t="n"/>
-      <c r="H20" s="7" t="n"/>
-      <c r="I20" s="20" t="n"/>
-      <c r="J20" s="8">
+      <c r="B20" s="91" t="n"/>
+      <c r="C20" s="91" t="n"/>
+      <c r="D20" s="95" t="n"/>
+      <c r="E20" s="91" t="n"/>
+      <c r="F20" s="91" t="n"/>
+      <c r="G20" s="95" t="n"/>
+      <c r="H20" s="96" t="n"/>
+      <c r="I20" s="97" t="n"/>
+      <c r="J20" s="98">
         <f>IF(OR(H20="",I20=""),"",H20*I20)</f>
         <v/>
       </c>
-      <c r="K20" s="7" t="n"/>
-      <c r="L20" s="7" t="n"/>
-      <c r="M20" s="8">
+      <c r="K20" s="96" t="n"/>
+      <c r="L20" s="96" t="n"/>
+      <c r="M20" s="98">
         <f>IF(J20="","",J20+N(K20)+N(L20))</f>
         <v/>
       </c>
-      <c r="N20" s="24" t="n"/>
+      <c r="N20" s="91" t="n"/>
     </row>
     <row r="21" ht="22.05" customHeight="1" s="34">
-      <c r="A21" s="5" t="n">
+      <c r="A21" s="94" t="n">
         <v>7</v>
       </c>
-      <c r="B21" s="24" t="n"/>
-      <c r="C21" s="24" t="n"/>
-      <c r="D21" s="5" t="n"/>
-      <c r="E21" s="24" t="n"/>
-      <c r="F21" s="24" t="n"/>
-      <c r="G21" s="5" t="n"/>
-      <c r="H21" s="7" t="n"/>
-      <c r="I21" s="20" t="n"/>
-      <c r="J21" s="8">
+      <c r="B21" s="91" t="n"/>
+      <c r="C21" s="91" t="n"/>
+      <c r="D21" s="95" t="n"/>
+      <c r="E21" s="91" t="n"/>
+      <c r="F21" s="91" t="n"/>
+      <c r="G21" s="95" t="n"/>
+      <c r="H21" s="96" t="n"/>
+      <c r="I21" s="97" t="n"/>
+      <c r="J21" s="98">
         <f>IF(OR(H21="",I21=""),"",H21*I21)</f>
         <v/>
       </c>
-      <c r="K21" s="7" t="n"/>
-      <c r="L21" s="7" t="n"/>
-      <c r="M21" s="8">
+      <c r="K21" s="96" t="n"/>
+      <c r="L21" s="96" t="n"/>
+      <c r="M21" s="98">
         <f>IF(J21="","",J21+N(K21)+N(L21))</f>
         <v/>
       </c>
-      <c r="N21" s="24" t="n"/>
+      <c r="N21" s="91" t="n"/>
     </row>
     <row r="22" ht="22.05" customHeight="1" s="34">
-      <c r="A22" s="5" t="n">
+      <c r="A22" s="94" t="n">
         <v>8</v>
       </c>
-      <c r="B22" s="24" t="n"/>
-      <c r="C22" s="24" t="n"/>
-      <c r="D22" s="5" t="n"/>
-      <c r="E22" s="24" t="n"/>
-      <c r="F22" s="24" t="n"/>
-      <c r="G22" s="5" t="n"/>
-      <c r="H22" s="7" t="n"/>
-      <c r="I22" s="20" t="n"/>
-      <c r="J22" s="8">
+      <c r="B22" s="91" t="n"/>
+      <c r="C22" s="91" t="n"/>
+      <c r="D22" s="95" t="n"/>
+      <c r="E22" s="91" t="n"/>
+      <c r="F22" s="91" t="n"/>
+      <c r="G22" s="95" t="n"/>
+      <c r="H22" s="96" t="n"/>
+      <c r="I22" s="97" t="n"/>
+      <c r="J22" s="98">
         <f>IF(OR(H22="",I22=""),"",H22*I22)</f>
         <v/>
       </c>
-      <c r="K22" s="7" t="n"/>
-      <c r="L22" s="7" t="n"/>
-      <c r="M22" s="8">
+      <c r="K22" s="96" t="n"/>
+      <c r="L22" s="96" t="n"/>
+      <c r="M22" s="98">
         <f>IF(J22="","",J22+N(K22)+N(L22))</f>
         <v/>
       </c>
-      <c r="N22" s="24" t="n"/>
+      <c r="N22" s="91" t="n"/>
     </row>
     <row r="23" ht="22.05" customHeight="1" s="34">
-      <c r="A23" s="5" t="n">
+      <c r="A23" s="94" t="n">
         <v>9</v>
       </c>
-      <c r="B23" s="24" t="n"/>
-      <c r="C23" s="24" t="n"/>
-      <c r="D23" s="5" t="n"/>
-      <c r="E23" s="24" t="n"/>
-      <c r="F23" s="24" t="n"/>
-      <c r="G23" s="5" t="n"/>
-      <c r="H23" s="7" t="n"/>
-      <c r="I23" s="20" t="n"/>
-      <c r="J23" s="8">
+      <c r="B23" s="91" t="n"/>
+      <c r="C23" s="91" t="n"/>
+      <c r="D23" s="95" t="n"/>
+      <c r="E23" s="91" t="n"/>
+      <c r="F23" s="91" t="n"/>
+      <c r="G23" s="95" t="n"/>
+      <c r="H23" s="96" t="n"/>
+      <c r="I23" s="97" t="n"/>
+      <c r="J23" s="98">
         <f>IF(OR(H23="",I23=""),"",H23*I23)</f>
         <v/>
       </c>
-      <c r="K23" s="7" t="n"/>
-      <c r="L23" s="7" t="n"/>
-      <c r="M23" s="8">
+      <c r="K23" s="96" t="n"/>
+      <c r="L23" s="96" t="n"/>
+      <c r="M23" s="98">
         <f>IF(J23="","",J23+N(K23)+N(L23))</f>
         <v/>
       </c>
-      <c r="N23" s="24" t="n"/>
+      <c r="N23" s="91" t="n"/>
     </row>
     <row r="24" ht="22.05" customHeight="1" s="34">
-      <c r="A24" s="5" t="n">
+      <c r="A24" s="94" t="n">
         <v>10</v>
       </c>
-      <c r="B24" s="24" t="n"/>
-      <c r="C24" s="24" t="n"/>
-      <c r="D24" s="5" t="n"/>
-      <c r="E24" s="24" t="n"/>
-      <c r="F24" s="24" t="n"/>
-      <c r="G24" s="5" t="n"/>
-      <c r="H24" s="7" t="n"/>
-      <c r="I24" s="20" t="n"/>
-      <c r="J24" s="8">
+      <c r="B24" s="91" t="n"/>
+      <c r="C24" s="91" t="n"/>
+      <c r="D24" s="95" t="n"/>
+      <c r="E24" s="91" t="n"/>
+      <c r="F24" s="91" t="n"/>
+      <c r="G24" s="95" t="n"/>
+      <c r="H24" s="96" t="n"/>
+      <c r="I24" s="97" t="n"/>
+      <c r="J24" s="98">
         <f>IF(OR(H24="",I24=""),"",H24*I24)</f>
         <v/>
       </c>
-      <c r="K24" s="7" t="n"/>
-      <c r="L24" s="7" t="n"/>
-      <c r="M24" s="8">
+      <c r="K24" s="96" t="n"/>
+      <c r="L24" s="96" t="n"/>
+      <c r="M24" s="98">
         <f>IF(J24="","",J24+N(K24)+N(L24))</f>
         <v/>
       </c>
-      <c r="N24" s="24" t="n"/>
+      <c r="N24" s="91" t="n"/>
     </row>
     <row r="25" ht="22.05" customHeight="1" s="34">
-      <c r="A25" s="5" t="n">
+      <c r="A25" s="94" t="n">
         <v>11</v>
       </c>
-      <c r="B25" s="24" t="n"/>
-      <c r="C25" s="24" t="n"/>
-      <c r="D25" s="5" t="n"/>
-      <c r="E25" s="24" t="n"/>
-      <c r="F25" s="24" t="n"/>
-      <c r="G25" s="5" t="n"/>
-      <c r="H25" s="7" t="n"/>
-      <c r="I25" s="20" t="n"/>
-      <c r="J25" s="8">
+      <c r="B25" s="91" t="n"/>
+      <c r="C25" s="91" t="n"/>
+      <c r="D25" s="95" t="n"/>
+      <c r="E25" s="91" t="n"/>
+      <c r="F25" s="91" t="n"/>
+      <c r="G25" s="95" t="n"/>
+      <c r="H25" s="96" t="n"/>
+      <c r="I25" s="97" t="n"/>
+      <c r="J25" s="98">
         <f>IF(OR(H25="",I25=""),"",H25*I25)</f>
         <v/>
       </c>
-      <c r="K25" s="7" t="n"/>
-      <c r="L25" s="7" t="n"/>
-      <c r="M25" s="8">
+      <c r="K25" s="96" t="n"/>
+      <c r="L25" s="96" t="n"/>
+      <c r="M25" s="98">
         <f>IF(J25="","",J25+N(K25)+N(L25))</f>
         <v/>
       </c>
-      <c r="N25" s="24" t="n"/>
+      <c r="N25" s="91" t="n"/>
     </row>
     <row r="26" ht="22.05" customHeight="1" s="34">
-      <c r="A26" s="5" t="n">
+      <c r="A26" s="94" t="n">
         <v>12</v>
       </c>
-      <c r="B26" s="24" t="n"/>
-      <c r="C26" s="24" t="n"/>
-      <c r="D26" s="5" t="n"/>
-      <c r="E26" s="24" t="n"/>
-      <c r="F26" s="24" t="n"/>
-      <c r="G26" s="5" t="n"/>
-      <c r="H26" s="7" t="n"/>
-      <c r="I26" s="20" t="n"/>
-      <c r="J26" s="8">
+      <c r="B26" s="91" t="n"/>
+      <c r="C26" s="91" t="n"/>
+      <c r="D26" s="95" t="n"/>
+      <c r="E26" s="91" t="n"/>
+      <c r="F26" s="91" t="n"/>
+      <c r="G26" s="95" t="n"/>
+      <c r="H26" s="96" t="n"/>
+      <c r="I26" s="97" t="n"/>
+      <c r="J26" s="98">
         <f>IF(OR(H26="",I26=""),"",H26*I26)</f>
         <v/>
       </c>
-      <c r="K26" s="7" t="n"/>
-      <c r="L26" s="7" t="n"/>
-      <c r="M26" s="8">
+      <c r="K26" s="96" t="n"/>
+      <c r="L26" s="96" t="n"/>
+      <c r="M26" s="98">
         <f>IF(J26="","",J26+N(K26)+N(L26))</f>
         <v/>
       </c>
-      <c r="N26" s="24" t="n"/>
+      <c r="N26" s="91" t="n"/>
     </row>
     <row r="27" ht="22.05" customHeight="1" s="34">
-      <c r="A27" s="5" t="n">
+      <c r="A27" s="94" t="n">
         <v>13</v>
       </c>
-      <c r="B27" s="24" t="n"/>
-      <c r="C27" s="24" t="n"/>
-      <c r="D27" s="5" t="n"/>
-      <c r="E27" s="24" t="n"/>
-      <c r="F27" s="24" t="n"/>
-      <c r="G27" s="5" t="n"/>
-      <c r="H27" s="7" t="n"/>
-      <c r="I27" s="20" t="n"/>
-      <c r="J27" s="8">
+      <c r="B27" s="91" t="n"/>
+      <c r="C27" s="91" t="n"/>
+      <c r="D27" s="95" t="n"/>
+      <c r="E27" s="91" t="n"/>
+      <c r="F27" s="91" t="n"/>
+      <c r="G27" s="95" t="n"/>
+      <c r="H27" s="96" t="n"/>
+      <c r="I27" s="97" t="n"/>
+      <c r="J27" s="98">
         <f>IF(OR(H27="",I27=""),"",H27*I27)</f>
         <v/>
       </c>
-      <c r="K27" s="7" t="n"/>
-      <c r="L27" s="7" t="n"/>
-      <c r="M27" s="8">
+      <c r="K27" s="96" t="n"/>
+      <c r="L27" s="96" t="n"/>
+      <c r="M27" s="98">
         <f>IF(J27="","",J27+N(K27)+N(L27))</f>
         <v/>
       </c>
-      <c r="N27" s="24" t="n"/>
+      <c r="N27" s="91" t="n"/>
     </row>
     <row r="28" ht="22.05" customHeight="1" s="34">
-      <c r="A28" s="5" t="n">
+      <c r="A28" s="94" t="n">
         <v>14</v>
       </c>
-      <c r="B28" s="24" t="n"/>
-      <c r="C28" s="24" t="n"/>
-      <c r="D28" s="5" t="n"/>
-      <c r="E28" s="24" t="n"/>
-      <c r="F28" s="24" t="n"/>
-      <c r="G28" s="5" t="n"/>
-      <c r="H28" s="7" t="n"/>
-      <c r="I28" s="20" t="n"/>
-      <c r="J28" s="8">
+      <c r="B28" s="91" t="n"/>
+      <c r="C28" s="91" t="n"/>
+      <c r="D28" s="95" t="n"/>
+      <c r="E28" s="91" t="n"/>
+      <c r="F28" s="91" t="n"/>
+      <c r="G28" s="95" t="n"/>
+      <c r="H28" s="96" t="n"/>
+      <c r="I28" s="97" t="n"/>
+      <c r="J28" s="98">
         <f>IF(OR(H28="",I28=""),"",H28*I28)</f>
         <v/>
       </c>
-      <c r="K28" s="7" t="n"/>
-      <c r="L28" s="7" t="n"/>
-      <c r="M28" s="8">
+      <c r="K28" s="96" t="n"/>
+      <c r="L28" s="96" t="n"/>
+      <c r="M28" s="98">
         <f>IF(J28="","",J28+N(K28)+N(L28))</f>
         <v/>
       </c>
-      <c r="N28" s="24" t="n"/>
+      <c r="N28" s="91" t="n"/>
     </row>
     <row r="29">
       <c r="A29" s="36" t="inlineStr">
@@ -1550,19 +1604,19 @@
       <c r="G29" s="90" t="n"/>
       <c r="H29" s="90" t="n"/>
       <c r="I29" s="84" t="n"/>
-      <c r="J29" s="86">
+      <c r="J29" s="99">
         <f>SUM(J15:J28)</f>
         <v/>
       </c>
-      <c r="K29" s="86">
+      <c r="K29" s="99">
         <f>SUM(K15:K28)</f>
         <v/>
       </c>
-      <c r="L29" s="86">
+      <c r="L29" s="99">
         <f>SUM(L15:L28)</f>
         <v/>
       </c>
-      <c r="M29" s="86">
+      <c r="M29" s="99">
         <f>SUM(M15:M28)</f>
         <v/>
       </c>
@@ -1589,7 +1643,7 @@
       <c r="M31" s="90" t="n"/>
       <c r="N31" s="84" t="n"/>
     </row>
-    <row r="32" ht="18" customHeight="1" s="34">
+    <row r="32" ht="29" customHeight="1" s="34">
       <c r="B32" s="31" t="inlineStr">
         <is>
           <t>Propiedad</t>
@@ -1606,7 +1660,7 @@
           <t>% del total</t>
         </is>
       </c>
-      <c r="G32" s="24" t="inlineStr">
+      <c r="G32" s="100" t="inlineStr">
         <is>
           <t>El «valor del equipo» es tarifa × cantidad usada. Para un equipo propio, use la tarifa interna de la empresa (depreciación, mantenimiento y seguros).
 El combustible y el operador se registran aparte para ver cuánto cuesta realmente cada máquina.</t>
@@ -1621,18 +1675,18 @@
       <c r="N32" s="48" t="n"/>
     </row>
     <row r="33" ht="18" customHeight="1" s="34">
-      <c r="A33" s="24" t="n"/>
+      <c r="A33" s="91" t="n"/>
       <c r="B33" s="22" t="inlineStr">
         <is>
           <t>Propio</t>
         </is>
       </c>
       <c r="C33" s="84" t="n"/>
-      <c r="D33" s="41">
+      <c r="D33" s="101">
         <f>SUMIF($D$15:$D$28,B33,$M$15:$M$28)</f>
         <v/>
       </c>
-      <c r="E33" s="13">
+      <c r="E33" s="102">
         <f>IF($M$29=0,"",D33/$M$29)</f>
         <v/>
       </c>
@@ -1640,18 +1694,18 @@
       <c r="N33" s="50" t="n"/>
     </row>
     <row r="34" ht="18" customHeight="1" s="34">
-      <c r="A34" s="24" t="n"/>
+      <c r="A34" s="91" t="n"/>
       <c r="B34" s="22" t="inlineStr">
         <is>
           <t>Alquilado</t>
         </is>
       </c>
       <c r="C34" s="84" t="n"/>
-      <c r="D34" s="41">
+      <c r="D34" s="101">
         <f>SUMIF($D$15:$D$28,B34,$M$15:$M$28)</f>
         <v/>
       </c>
-      <c r="E34" s="13">
+      <c r="E34" s="102">
         <f>IF($M$29=0,"",D34/$M$29)</f>
         <v/>
       </c>
@@ -1666,11 +1720,11 @@
       </c>
       <c r="B35" s="90" t="n"/>
       <c r="C35" s="84" t="n"/>
-      <c r="D35" s="86">
+      <c r="D35" s="99">
         <f>SUM(D33:D34)</f>
         <v/>
       </c>
-      <c r="E35" s="15">
+      <c r="E35" s="103">
         <f>IF(D35=0,"",1)</f>
         <v/>
       </c>
@@ -1736,10 +1790,10 @@
       </c>
       <c r="B39" s="90" t="n"/>
       <c r="C39" s="84" t="n"/>
-      <c r="D39" s="24" t="n"/>
-      <c r="E39" s="90" t="n"/>
-      <c r="F39" s="90" t="n"/>
-      <c r="G39" s="84" t="n"/>
+      <c r="D39" s="91" t="n"/>
+      <c r="E39" s="92" t="n"/>
+      <c r="F39" s="92" t="n"/>
+      <c r="G39" s="93" t="n"/>
       <c r="H39" s="22" t="inlineStr">
         <is>
           <t>Firma:</t>
@@ -1747,10 +1801,10 @@
       </c>
       <c r="I39" s="90" t="n"/>
       <c r="J39" s="84" t="n"/>
-      <c r="K39" s="24" t="n"/>
-      <c r="L39" s="90" t="n"/>
-      <c r="M39" s="90" t="n"/>
-      <c r="N39" s="84" t="n"/>
+      <c r="K39" s="91" t="n"/>
+      <c r="L39" s="92" t="n"/>
+      <c r="M39" s="92" t="n"/>
+      <c r="N39" s="93" t="n"/>
     </row>
     <row r="40" ht="15" customHeight="1" s="34">
       <c r="A40" s="22" t="inlineStr">
@@ -1760,10 +1814,10 @@
       </c>
       <c r="B40" s="90" t="n"/>
       <c r="C40" s="84" t="n"/>
-      <c r="D40" s="24" t="n"/>
-      <c r="E40" s="90" t="n"/>
-      <c r="F40" s="90" t="n"/>
-      <c r="G40" s="84" t="n"/>
+      <c r="D40" s="91" t="n"/>
+      <c r="E40" s="92" t="n"/>
+      <c r="F40" s="92" t="n"/>
+      <c r="G40" s="93" t="n"/>
       <c r="H40" s="22" t="inlineStr">
         <is>
           <t>Nombre:</t>
@@ -1771,10 +1825,10 @@
       </c>
       <c r="I40" s="90" t="n"/>
       <c r="J40" s="84" t="n"/>
-      <c r="K40" s="24" t="n"/>
-      <c r="L40" s="90" t="n"/>
-      <c r="M40" s="90" t="n"/>
-      <c r="N40" s="84" t="n"/>
+      <c r="K40" s="91" t="n"/>
+      <c r="L40" s="92" t="n"/>
+      <c r="M40" s="92" t="n"/>
+      <c r="N40" s="93" t="n"/>
     </row>
     <row r="41" ht="15" customHeight="1" s="34">
       <c r="A41" s="22" t="inlineStr">
@@ -1784,10 +1838,10 @@
       </c>
       <c r="B41" s="90" t="n"/>
       <c r="C41" s="84" t="n"/>
-      <c r="D41" s="24" t="n"/>
-      <c r="E41" s="90" t="n"/>
-      <c r="F41" s="90" t="n"/>
-      <c r="G41" s="84" t="n"/>
+      <c r="D41" s="91" t="n"/>
+      <c r="E41" s="92" t="n"/>
+      <c r="F41" s="92" t="n"/>
+      <c r="G41" s="93" t="n"/>
       <c r="H41" s="22" t="inlineStr">
         <is>
           <t>Cargo:</t>
@@ -1795,12 +1849,13 @@
       </c>
       <c r="I41" s="90" t="n"/>
       <c r="J41" s="84" t="n"/>
-      <c r="K41" s="24" t="n"/>
-      <c r="L41" s="90" t="n"/>
-      <c r="M41" s="90" t="n"/>
-      <c r="N41" s="84" t="n"/>
+      <c r="K41" s="91" t="n"/>
+      <c r="L41" s="92" t="n"/>
+      <c r="M41" s="92" t="n"/>
+      <c r="N41" s="93" t="n"/>
     </row>
   </sheetData>
+  <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="0" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="0" sort="1"/>
   <mergeCells count="50">
     <mergeCell ref="A9:N9"/>
     <mergeCell ref="A41:C41"/>
